--- a/data/Scene.xlsx
+++ b/data/Scene.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,24 +440,31 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5"/>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -465,7 +472,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
@@ -473,7 +480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -481,7 +488,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -489,7 +496,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -497,7 +504,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -505,7 +512,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -513,7 +520,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -521,7 +528,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -529,7 +536,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -537,7 +544,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -545,7 +552,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
@@ -553,7 +560,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -561,7 +568,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -569,7 +576,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" t="n">
         <v>0</v>
@@ -577,17 +584,9 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B23" t="n">
         <v>1</v>
       </c>
     </row>
